--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4268" uniqueCount="636">
   <si>
     <t>Property</t>
   </si>
@@ -1476,6 +1476,524 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/link-type|4.0.1</t>
+  </si>
+  <si>
+    <t>stockholm-genomic-specimen</t>
+  </si>
+  <si>
+    <t>https://fhir.inera.se/ig/template/StructureDefinition/stockholm-genomic-specimen</t>
+  </si>
+  <si>
+    <t>StockholmGenomicSpecimen</t>
+  </si>
+  <si>
+    <t>Stockholm Genomic Specimen</t>
+  </si>
+  <si>
+    <t>2026-10-30T09:20:10+00:00</t>
+  </si>
+  <si>
+    <t>Profile to store the data about the specimen used in the genomic study. It is also used to relate both procedures and result files to a certain specimen.</t>
+  </si>
+  <si>
+    <t>The purpose of this profile is to represent the specimen used in the genomic study. It is used to relate patients, procedures and result files to a certain specimen.</t>
+  </si>
+  <si>
+    <t>Specimen</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Specimen</t>
+  </si>
+  <si>
+    <t>Sample for analysis</t>
+  </si>
+  <si>
+    <t>A sample to be used for analysis.</t>
+  </si>
+  <si>
+    <t>Specimen.id</t>
+  </si>
+  <si>
+    <t>Specimen.meta</t>
+  </si>
+  <si>
+    <t>Specimen.implicitRules</t>
+  </si>
+  <si>
+    <t>Specimen.language</t>
+  </si>
+  <si>
+    <t>Specimen.text</t>
+  </si>
+  <si>
+    <t>Specimen.contained</t>
+  </si>
+  <si>
+    <t>Specimen.extension</t>
+  </si>
+  <si>
+    <t>Specimen.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.identifier</t>
+  </si>
+  <si>
+    <t>Requester and laboratory specimen identifiers</t>
+  </si>
+  <si>
+    <t>The identifier of the specimen. This is a required element and should always be populated when using this profile.</t>
+  </si>
+  <si>
+    <t>Two identifiers are used to identify the specimen, one assigned by the requester and one assigned by the laboratory. The identifier can be used for both the requester and the laboratory as a search parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:type.coding.code}
+</t>
+  </si>
+  <si>
+    <t>closed</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:requester-sample-identifier</t>
+  </si>
+  <si>
+    <t>requester-sample-identifier</t>
+  </si>
+  <si>
+    <t>External Identifier</t>
+  </si>
+  <si>
+    <t>Id for specimen.</t>
+  </si>
+  <si>
+    <t>Specimen.identifier:laboratory-sample-identifier</t>
+  </si>
+  <si>
+    <t>laboratory-sample-identifier</t>
+  </si>
+  <si>
+    <t>Specimen.accessionIdentifier</t>
+  </si>
+  <si>
+    <t>Identifier assigned by the lab</t>
+  </si>
+  <si>
+    <t>The identifier assigned by the lab when accessioning specimen(s). This is not necessarily the same as the specimen identifier, depending on local lab procedures.</t>
+  </si>
+  <si>
+    <t>Specimen.status</t>
+  </si>
+  <si>
+    <t>available | unavailable | unsatisfactory | entered-in-error</t>
+  </si>
+  <si>
+    <t>The availability of the specimen.</t>
+  </si>
+  <si>
+    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>Codes providing the status/availability of a specimen.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-status|4.0.1</t>
+  </si>
+  <si>
+    <t>Specimen.type</t>
+  </si>
+  <si>
+    <t>Kind of material that forms the specimen</t>
+  </si>
+  <si>
+    <t>The kind of material that forms the specimen.</t>
+  </si>
+  <si>
+    <t>The type can change the way that a specimen is handled and drives what kind of analyses can properly be performed on the specimen. It is frequently used in diagnostic work flow decision making systems.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>The type of the specimen.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0487</t>
+  </si>
+  <si>
+    <t>Specimen.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Substance|4.0.1|Location|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device</t>
+  </si>
+  <si>
+    <t>Where the specimen came from. This may be from patient(s), from a location (e.g., the source of an environmental sample), or a sampling of a substance or a device.</t>
+  </si>
+  <si>
+    <t>Must know the subject context.</t>
+  </si>
+  <si>
+    <t>Specimen.receivedTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>The time when specimen was received for processing</t>
+  </si>
+  <si>
+    <t>Time when specimen was received for processing or testing.</t>
+  </si>
+  <si>
+    <t>Specimen.parent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Specimen from which this specimen originated</t>
+  </si>
+  <si>
+    <t>Reference to the parent (source) specimen which is used when the specimen was either derived from or a component of another specimen.</t>
+  </si>
+  <si>
+    <t>The parent specimen could be the source from which the current specimen is derived by some processing step (e.g. an aliquot or isolate or extracted nucleic acids from clinical samples) or one of many specimens that were combined to create a pooled sample.</t>
+  </si>
+  <si>
+    <t>Specimen.request</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Why the specimen was collected</t>
+  </si>
+  <si>
+    <t>Details concerning a service request that required a specimen to be collected.</t>
+  </si>
+  <si>
+    <t>The request may be explicit or implied such with a ServiceRequest that requires a blood draw.</t>
+  </si>
+  <si>
+    <t>Specimen.collection</t>
+  </si>
+  <si>
+    <t>Collection details</t>
+  </si>
+  <si>
+    <t>Details concerning the specimen collection.</t>
+  </si>
+  <si>
+    <t>Specimen.collection.id</t>
+  </si>
+  <si>
+    <t>Specimen.collection.extension</t>
+  </si>
+  <si>
+    <t>Specimen.collection.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.collection.collector</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Who collected the specimen</t>
+  </si>
+  <si>
+    <t>Person who collected the specimen.</t>
+  </si>
+  <si>
+    <t>Specimen.collection.collected[x]</t>
+  </si>
+  <si>
+    <t>dateTime
+Period</t>
+  </si>
+  <si>
+    <t>Collection time</t>
+  </si>
+  <si>
+    <t>Time when specimen was collected from subject - the physiologically relevant time.</t>
+  </si>
+  <si>
+    <t>Specimen.collection.duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
+  </si>
+  <si>
+    <t>How long it took to collect specimen</t>
+  </si>
+  <si>
+    <t>The span of time over which the collection of a specimen occurred.</t>
+  </si>
+  <si>
+    <t>Specimen.collection.quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+</t>
+  </si>
+  <si>
+    <t>The quantity of specimen collected</t>
+  </si>
+  <si>
+    <t>The quantity of specimen collected; for instance the volume of a blood sample, or the physical measurement of an anatomic pathology sample.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
+  </si>
+  <si>
+    <t>Specimen.collection.method</t>
+  </si>
+  <si>
+    <t>Technique used to perform collection</t>
+  </si>
+  <si>
+    <t>A coded value specifying the technique that is used to perform the procedure.</t>
+  </si>
+  <si>
+    <t>The  technique that is used to perform the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
+  </si>
+  <si>
+    <t>Specimen.collection.bodySite</t>
+  </si>
+  <si>
+    <t>Anatomical collection site</t>
+  </si>
+  <si>
+    <t>Anatomical location from which the specimen was collected (if subject is a patient). This is the target site.  This element is not used for environmental specimens.</t>
+  </si>
+  <si>
+    <t>If the use case requires  BodySite to be handled as a separate resource instead of an inline coded element (e.g. to identify and track separately)  then use the standard extension [bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+  </si>
+  <si>
+    <t>Specimen.collection.fastingStatus[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Duration</t>
+  </si>
+  <si>
+    <t>Whether or how long patient abstained from food and/or drink</t>
+  </si>
+  <si>
+    <t>Abstinence or reduction from some or all food, drink, or both, for a period of time prior to sample collection.</t>
+  </si>
+  <si>
+    <t>Representing fasting status using this element is preferred to representing it with an observation using a 'pre-coordinated code'  such as  LOINC 2005-7 (Calcium [Moles/​time] in 2 hour Urine --12 hours fasting), or  using  a component observation ` such as `Observation.component code`  = LOINC 49541-6 (Fasting status - Reported).</t>
+  </si>
+  <si>
+    <t>Many diagnostic tests require fasting  to facilitate accurate interpretation.</t>
+  </si>
+  <si>
+    <t>Codes describing the fasting status of the patient.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0916</t>
+  </si>
+  <si>
+    <t>Specimen.processing</t>
+  </si>
+  <si>
+    <t>Processing and processing step details</t>
+  </si>
+  <si>
+    <t>Details concerning processing and processing steps for the specimen.</t>
+  </si>
+  <si>
+    <t>Specimen.processing.id</t>
+  </si>
+  <si>
+    <t>Specimen.processing.extension</t>
+  </si>
+  <si>
+    <t>Specimen.processing.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.processing.description</t>
+  </si>
+  <si>
+    <t>Textual description of procedure</t>
+  </si>
+  <si>
+    <t>Textual description of procedure.</t>
+  </si>
+  <si>
+    <t>Specimen.processing.procedure</t>
+  </si>
+  <si>
+    <t>Indicates the treatment step  applied to the specimen</t>
+  </si>
+  <si>
+    <t>A coded value specifying the procedure used to process the specimen.</t>
+  </si>
+  <si>
+    <t>Type indicating the technique used to process the specimen.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
+  </si>
+  <si>
+    <t>Specimen.processing.additive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Substance|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Material used in the processing step</t>
+  </si>
+  <si>
+    <t>Material used in the processing step.</t>
+  </si>
+  <si>
+    <t>Specimen.processing.time[x]</t>
+  </si>
+  <si>
+    <t>Date and time of specimen processing</t>
+  </si>
+  <si>
+    <t>A record of the time or period when the specimen processing occurred.  For example the time of sample fixation or the period of time the sample was in formalin.</t>
+  </si>
+  <si>
+    <t>Specimen.container</t>
+  </si>
+  <si>
+    <t>Direct container of specimen (tube/slide, etc.)</t>
+  </si>
+  <si>
+    <t>The container holding the specimen.  The recursive nature of containers; i.e. blood in tube in tray in rack is not addressed here.</t>
+  </si>
+  <si>
+    <t>Specimen.container.id</t>
+  </si>
+  <si>
+    <t>Specimen.container.extension</t>
+  </si>
+  <si>
+    <t>Specimen.container.modifierExtension</t>
+  </si>
+  <si>
+    <t>Specimen.container.identifier</t>
+  </si>
+  <si>
+    <t>Id for the container</t>
+  </si>
+  <si>
+    <t>Id for container. There may be multiple; a manufacturer's bar code, lab assigned identifier, etc. The container ID may differ from the specimen id in some circumstances.</t>
+  </si>
+  <si>
+    <t>Specimen.container.description</t>
+  </si>
+  <si>
+    <t>Textual description of the container</t>
+  </si>
+  <si>
+    <t>Textual description of the container.</t>
+  </si>
+  <si>
+    <t>Specimen.container.type</t>
+  </si>
+  <si>
+    <t>Kind of container directly associated with specimen</t>
+  </si>
+  <si>
+    <t>The type of container associated with the specimen (e.g. slide, aliquot, etc.).</t>
+  </si>
+  <si>
+    <t>Type of specimen container.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
+  </si>
+  <si>
+    <t>Specimen.container.capacity</t>
+  </si>
+  <si>
+    <t>Container volume or size</t>
+  </si>
+  <si>
+    <t>The capacity (volume or other measure) the container may contain.</t>
+  </si>
+  <si>
+    <t>Specimen.container.specimenQuantity</t>
+  </si>
+  <si>
+    <t>Quantity of specimen within container</t>
+  </si>
+  <si>
+    <t>The quantity of specimen in the container; may be volume, dimensions, or other appropriate measurements, depending on the specimen type.</t>
+  </si>
+  <si>
+    <t>Specimen.container.additive[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Reference(Substance|4.0.1)</t>
+  </si>
+  <si>
+    <t>Additive associated with container</t>
+  </si>
+  <si>
+    <t>Introduced substance to preserve, maintain or enhance the specimen. Examples: Formalin, Citrate, EDTA.</t>
+  </si>
+  <si>
+    <t>Substance added to specimen container.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0371</t>
+  </si>
+  <si>
+    <t>Specimen.condition</t>
+  </si>
+  <si>
+    <t>State of the specimen</t>
+  </si>
+  <si>
+    <t>A mode or state of being that describes the nature of the specimen.</t>
+  </si>
+  <si>
+    <t>Specimen condition is an observation made about the specimen.  It's a point-in-time assessment.  It can be used to assess its quality or appropriateness for a specific test.</t>
+  </si>
+  <si>
+    <t>The specimen condition can be used to assess its quality or appropriateness for a specific test.</t>
+  </si>
+  <si>
+    <t>Codes describing the state of the specimen.</t>
+  </si>
+  <si>
+    <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
+  </si>
+  <si>
+    <t>Specimen.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>To communicate any details or issues about the specimen or during the specimen collection. (for example: broken vial, sent with patient, frozen).</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +2127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1786,6 +2304,170 @@
         <v>38</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>12</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>14</v>
+      </c>
+      <c r="B30" s="2"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>26</v>
+      </c>
+      <c r="B37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>27</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>29</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1793,13 +2475,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK76"/>
+  <dimension ref="A1:AK126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.92578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="34.765625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="24.4609375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.76171875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="33.83984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.94921875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="22.921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="34.21875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -1822,13 +2504,13 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="48.33203125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="52.27734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="20.2734375" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="29.88671875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="31.46875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.046875" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
   </cols>
@@ -9843,6 +10525,5214 @@
         <v>96</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="D77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F77" s="2"/>
+      <c r="G77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R77" s="2"/>
+      <c r="S77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="D78" s="2"/>
+      <c r="E78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F78" s="2"/>
+      <c r="G78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="P78" s="2"/>
+      <c r="Q78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R78" s="2"/>
+      <c r="S78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="D79" s="2"/>
+      <c r="E79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F79" s="2"/>
+      <c r="G79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R79" s="2"/>
+      <c r="S79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="D80" s="2"/>
+      <c r="E80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F80" s="2"/>
+      <c r="G80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="P80" s="2"/>
+      <c r="Q80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R80" s="2"/>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="D81" s="2"/>
+      <c r="E81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F81" s="2"/>
+      <c r="G81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="P81" s="2"/>
+      <c r="Q81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R81" s="2"/>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="D82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="F82" s="2"/>
+      <c r="G82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="P82" s="2"/>
+      <c r="Q82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R82" s="2"/>
+      <c r="S82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="D83" s="2"/>
+      <c r="E83" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="F83" s="2"/>
+      <c r="G83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="P83" s="2"/>
+      <c r="Q83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R83" s="2"/>
+      <c r="S83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="C84" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="D84" s="2"/>
+      <c r="E84" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F84" s="2"/>
+      <c r="G84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P84" s="2"/>
+      <c r="Q84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R84" s="2"/>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F85" s="2"/>
+      <c r="G85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R85" s="2"/>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="D86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F86" s="2"/>
+      <c r="G86" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="Q86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R86" s="2"/>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="AD86" s="2"/>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="C87" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="D87" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="E87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F87" s="2"/>
+      <c r="G87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R87" s="2"/>
+      <c r="S87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C88" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="D88" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="E88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F88" s="2"/>
+      <c r="G88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="O88" s="2"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R88" s="2"/>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="D89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F89" s="2"/>
+      <c r="G89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R89" s="2"/>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="D90" s="2"/>
+      <c r="E90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F90" s="2"/>
+      <c r="G90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="P90" s="2"/>
+      <c r="Q90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R90" s="2"/>
+      <c r="S90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="D91" s="2"/>
+      <c r="E91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F91" s="2"/>
+      <c r="G91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="P91" s="2"/>
+      <c r="Q91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R91" s="2"/>
+      <c r="S91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="D92" s="2"/>
+      <c r="E92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F92" s="2"/>
+      <c r="G92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="Q92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R92" s="2"/>
+      <c r="S92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C93" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="D93" s="2"/>
+      <c r="E93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F93" s="2"/>
+      <c r="G93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O93" s="2"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R93" s="2"/>
+      <c r="S93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="D94" s="2"/>
+      <c r="E94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F94" s="2"/>
+      <c r="G94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="P94" s="2"/>
+      <c r="Q94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R94" s="2"/>
+      <c r="S94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="D95" s="2"/>
+      <c r="E95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F95" s="2"/>
+      <c r="G95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="P95" s="2"/>
+      <c r="Q95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R95" s="2"/>
+      <c r="S95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="D96" s="2"/>
+      <c r="E96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F96" s="2"/>
+      <c r="G96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R96" s="2"/>
+      <c r="S96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C97" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="D97" s="2"/>
+      <c r="E97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F97" s="2"/>
+      <c r="G97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" s="2"/>
+      <c r="Q97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R97" s="2"/>
+      <c r="S97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C98" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="D98" s="2"/>
+      <c r="E98" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F98" s="2"/>
+      <c r="G98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P98" s="2"/>
+      <c r="Q98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R98" s="2"/>
+      <c r="S98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="C99" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="D99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F99" s="2"/>
+      <c r="G99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R99" s="2"/>
+      <c r="S99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C100" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="D100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F100" s="2"/>
+      <c r="G100" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R100" s="2"/>
+      <c r="S100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="C101" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="D101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F101" s="2"/>
+      <c r="G101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="O101" s="2"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R101" s="2"/>
+      <c r="S101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C102" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="D102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F102" s="2"/>
+      <c r="G102" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R102" s="2"/>
+      <c r="S102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C103" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="D103" s="2"/>
+      <c r="E103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F103" s="2"/>
+      <c r="G103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R103" s="2"/>
+      <c r="S103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="D104" s="2"/>
+      <c r="E104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F104" s="2"/>
+      <c r="G104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O104" s="2"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R104" s="2"/>
+      <c r="S104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="C105" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="D105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F105" s="2"/>
+      <c r="G105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="P105" s="2"/>
+      <c r="Q105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R105" s="2"/>
+      <c r="S105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="C106" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="D106" s="2"/>
+      <c r="E106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F106" s="2"/>
+      <c r="G106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="Q106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R106" s="2"/>
+      <c r="S106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="C107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="D107" s="2"/>
+      <c r="E107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F107" s="2"/>
+      <c r="G107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" s="2"/>
+      <c r="Q107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R107" s="2"/>
+      <c r="S107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="C108" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="D108" s="2"/>
+      <c r="E108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F108" s="2"/>
+      <c r="G108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O108" s="2"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R108" s="2"/>
+      <c r="S108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C109" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="D109" s="2"/>
+      <c r="E109" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F109" s="2"/>
+      <c r="G109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P109" s="2"/>
+      <c r="Q109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R109" s="2"/>
+      <c r="S109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="C110" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="D110" s="2"/>
+      <c r="E110" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F110" s="2"/>
+      <c r="G110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P110" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R110" s="2"/>
+      <c r="S110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="C111" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="D111" s="2"/>
+      <c r="E111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F111" s="2"/>
+      <c r="G111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" s="2"/>
+      <c r="Q111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R111" s="2"/>
+      <c r="S111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C112" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="D112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F112" s="2"/>
+      <c r="G112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="N112" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O112" s="2"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R112" s="2"/>
+      <c r="S112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C113" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="D113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F113" s="2"/>
+      <c r="G113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="N113" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2"/>
+      <c r="Q113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R113" s="2"/>
+      <c r="S113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C114" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="D114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F114" s="2"/>
+      <c r="G114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N114" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R114" s="2"/>
+      <c r="S114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="C115" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="D115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F115" s="2"/>
+      <c r="G115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N115" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="O115" s="2"/>
+      <c r="P115" s="2"/>
+      <c r="Q115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R115" s="2"/>
+      <c r="S115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="D116" s="2"/>
+      <c r="E116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F116" s="2"/>
+      <c r="G116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N116" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="O116" s="2"/>
+      <c r="P116" s="2"/>
+      <c r="Q116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R116" s="2"/>
+      <c r="S116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="D117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="F117" s="2"/>
+      <c r="G117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O117" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P117" s="2"/>
+      <c r="Q117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R117" s="2"/>
+      <c r="S117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C118" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="D118" s="2"/>
+      <c r="E118" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="F118" s="2"/>
+      <c r="G118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="Q118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R118" s="2"/>
+      <c r="S118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C119" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="D119" s="2"/>
+      <c r="E119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F119" s="2"/>
+      <c r="G119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="O119" s="2"/>
+      <c r="P119" s="2"/>
+      <c r="Q119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R119" s="2"/>
+      <c r="S119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="C120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="D120" s="2"/>
+      <c r="E120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F120" s="2"/>
+      <c r="G120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R120" s="2"/>
+      <c r="S120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="D121" s="2"/>
+      <c r="E121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F121" s="2"/>
+      <c r="G121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" s="2"/>
+      <c r="Q121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R121" s="2"/>
+      <c r="S121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C122" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="D122" s="2"/>
+      <c r="E122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F122" s="2"/>
+      <c r="G122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="N122" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R122" s="2"/>
+      <c r="S122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="D123" s="2"/>
+      <c r="E123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F123" s="2"/>
+      <c r="G123" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2"/>
+      <c r="Q123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R123" s="2"/>
+      <c r="S123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="D124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F124" s="2"/>
+      <c r="G124" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N124" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="O124" s="2"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R124" s="2"/>
+      <c r="S124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B125" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C125" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="D125" s="2"/>
+      <c r="E125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F125" s="2"/>
+      <c r="G125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K125" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L125" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M125" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="P125" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="Q125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R125" s="2"/>
+      <c r="S125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Z125" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="AA125" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AB125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG125" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AH125" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI125" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ125" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK125" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="D126" s="2"/>
+      <c r="E126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="F126" s="2"/>
+      <c r="G126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L126" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M126" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="N126" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="O126" s="2"/>
+      <c r="P126" s="2"/>
+      <c r="Q126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="R126" s="2"/>
+      <c r="S126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AG126" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
